--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2885-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2885-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9911FC4-832F-49FA-90F5-2572E31BFBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A665196E-AB94-47DB-B3B9-F173DB32C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0DD87566-D2DF-4B34-B32B-D27D83AAD777}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{182C041F-7D4F-4BFF-8FFF-0C23ED7F5FCC}"/>
   </bookViews>
   <sheets>
     <sheet name="2885-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,27 +1571,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CEF39F-0D84-46C8-90A1-F52B49AB29A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A53C2E9-E859-4FC1-9764-D8838A2C4F6F}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1625,7 +1624,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1661,7 +1660,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1713,7 +1712,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1781,7 +1780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="41"/>
       <c r="C6" s="13" t="s">
@@ -1881,7 +1880,7 @@
       <c r="W6" s="47"/>
       <c r="X6" s="43"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>2023</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="50"/>
       <c r="B8" s="51"/>
       <c r="C8" s="16" t="s">
@@ -1981,7 +1980,7 @@
       <c r="W8" s="57"/>
       <c r="X8" s="53"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2022</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40"/>
       <c r="B10" s="41"/>
       <c r="C10" s="13" t="s">
@@ -2081,7 +2080,7 @@
       <c r="W10" s="47"/>
       <c r="X10" s="43"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>2021</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="50"/>
       <c r="B12" s="51"/>
       <c r="C12" s="16" t="s">
@@ -2181,7 +2180,7 @@
       <c r="W12" s="57"/>
       <c r="X12" s="53"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>2020</v>
       </c>
@@ -2253,7 +2252,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>2019</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="50"/>
       <c r="B15" s="51"/>
       <c r="C15" s="16" t="s">
@@ -2353,7 +2352,7 @@
       <c r="W15" s="57"/>
       <c r="X15" s="53"/>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="58">
         <v>2018</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="60">
         <v>2017</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="58">
         <v>2016</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="60">
         <v>2015</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2014</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="41"/>
       <c r="C21" s="13" t="s">
@@ -2741,7 +2740,7 @@
       <c r="W21" s="47"/>
       <c r="X21" s="43"/>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>2013</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="50"/>
       <c r="B23" s="51"/>
       <c r="C23" s="16" t="s">
@@ -2841,7 +2840,7 @@
       <c r="W23" s="57"/>
       <c r="X23" s="53"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="58">
         <v>2012</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="60">
         <v>2011</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="58">
         <v>2010</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="60">
         <v>2009</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="58">
         <v>2008</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="60">
         <v>2007</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="58">
         <v>2006</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="60">
         <v>2005</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="58">
         <v>2004</v>
       </c>
@@ -3489,7 +3488,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="48">
         <v>2003</v>
       </c>
@@ -3561,7 +3560,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="50"/>
       <c r="B34" s="51"/>
       <c r="C34" s="16" t="s">
@@ -3589,7 +3588,7 @@
       <c r="W34" s="57"/>
       <c r="X34" s="53"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="58">
         <v>2002</v>
       </c>
@@ -3661,7 +3660,7 @@
         <v>7.77</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="60" t="s">
         <v>58</v>
       </c>
